--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2530,27 +2530,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131843000</v>
+        <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58131</v>
+        <v>58552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103023</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2560,27 +2560,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514180</v>
+        <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6583942</v>
+        <v>6584143</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2604,22 +2604,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2634,55 +2624,59 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Wedholm</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Wedholm</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131843000</t>
+          <t>https://artportalen.se/Sighting/137010691</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124893046</v>
+        <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>5199</v>
+        <v>58448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>102999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2691,13 +2685,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514014</v>
+        <v>514221</v>
       </c>
       <c r="R18" t="n">
-        <v>6584124</v>
+        <v>6583928</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2721,12 +2715,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2737,74 +2731,63 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124893046</t>
+          <t>https://artportalen.se/Sighting/137010772</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124893050</v>
+        <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>58293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>103012</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2813,13 +2796,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514010</v>
+        <v>514156</v>
       </c>
       <c r="R19" t="n">
-        <v>6583953</v>
+        <v>6583833</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2843,12 +2826,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,93 +2842,78 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124893050</t>
+          <t>https://artportalen.se/Sighting/137010683</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124893139</v>
+        <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>8444</v>
+        <v>58293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>103012</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514210</v>
+        <v>514164</v>
       </c>
       <c r="R20" t="n">
-        <v>6583882</v>
+        <v>6584147</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2969,12 +2937,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,91 +2951,65 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124893139</t>
+          <t>https://artportalen.se/Sighting/137010694</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128848257</v>
+        <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>56823</v>
+        <v>58293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>103012</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3076,13 +3018,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514136</v>
+        <v>514210</v>
       </c>
       <c r="R21" t="n">
-        <v>6583960</v>
+        <v>6583839</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3106,22 +3048,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>01:15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3136,27 +3068,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848257</t>
+          <t>https://artportalen.se/Sighting/137010751</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128848270</v>
+        <v>131843000</v>
       </c>
       <c r="B22" t="n">
-        <v>56823</v>
+        <v>58131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,53 +3096,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205992</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ölmbrotorp, Nrk</t>
+          <t>Ölmbrotorp, Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514046</v>
+        <v>514180</v>
       </c>
       <c r="R22" t="n">
-        <v>6583983</v>
+        <v>6583942</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3237,22 +3159,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3267,27 +3189,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Per Wedholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848270</t>
+          <t>https://artportalen.se/Sighting/131843000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128848285</v>
+        <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>56823</v>
+        <v>58164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,41 +3217,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205992</v>
+        <v>103023</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3338,13 +3250,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514155</v>
+        <v>514216</v>
       </c>
       <c r="R23" t="n">
-        <v>6583896</v>
+        <v>6584004</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3368,22 +3280,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3398,69 +3300,59 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848285</t>
+          <t>https://artportalen.se/Sighting/137010759</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128848292</v>
+        <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>56823</v>
+        <v>58731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>103055</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3469,13 +3361,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514148</v>
+        <v>514160</v>
       </c>
       <c r="R24" t="n">
-        <v>6583896</v>
+        <v>6584106</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3499,22 +3391,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3529,27 +3411,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848292</t>
+          <t>https://artportalen.se/Sighting/137010688</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128848254</v>
+        <v>124893046</v>
       </c>
       <c r="B25" t="n">
-        <v>56835</v>
+        <v>5199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3557,41 +3439,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>205995</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3600,10 +3468,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514136</v>
+        <v>514014</v>
       </c>
       <c r="R25" t="n">
-        <v>6583960</v>
+        <v>6584124</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3630,22 +3498,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>01:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3656,31 +3514,46 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848254</t>
+          <t>https://artportalen.se/Sighting/124893046</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128848268</v>
+        <v>124893050</v>
       </c>
       <c r="B26" t="n">
-        <v>56835</v>
+        <v>5199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,41 +3561,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>205995</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>autobox</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3731,13 +3590,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514046</v>
+        <v>514010</v>
       </c>
       <c r="R26" t="n">
-        <v>6583983</v>
+        <v>6583953</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3761,22 +3620,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3787,31 +3636,46 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848268</t>
+          <t>https://artportalen.se/Sighting/124893050</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128848283</v>
+        <v>124893139</v>
       </c>
       <c r="B27" t="n">
-        <v>56835</v>
+        <v>8444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3819,53 +3683,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205995</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>aktiv</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514157</v>
+        <v>514210</v>
       </c>
       <c r="R27" t="n">
-        <v>6583896</v>
+        <v>6583882</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3892,22 +3746,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>21:15</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3916,33 +3760,49 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848283</t>
+          <t>https://artportalen.se/Sighting/124893139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128848290</v>
+        <v>128848257</v>
       </c>
       <c r="B28" t="n">
-        <v>56835</v>
+        <v>56823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3950,26 +3810,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3984,7 +3844,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3993,13 +3853,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514151</v>
+        <v>514136</v>
       </c>
       <c r="R28" t="n">
-        <v>6583896</v>
+        <v>6583960</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4023,22 +3883,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4064,43 +3924,43 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848290</t>
+          <t>https://artportalen.se/Sighting/128848257</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128848250</v>
+        <v>128848270</v>
       </c>
       <c r="B29" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4115,7 +3975,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ultraljudsdetektor</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4124,13 +3984,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514136</v>
+        <v>514046</v>
       </c>
       <c r="R29" t="n">
-        <v>6583960</v>
+        <v>6583983</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4154,7 +4014,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -4169,7 +4029,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4195,43 +4055,43 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848250</t>
+          <t>https://artportalen.se/Sighting/128848270</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128848265</v>
+        <v>128848285</v>
       </c>
       <c r="B30" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4255,10 +4115,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514046</v>
+        <v>514155</v>
       </c>
       <c r="R30" t="n">
-        <v>6583983</v>
+        <v>6583896</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4326,43 +4186,43 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848265</t>
+          <t>https://artportalen.se/Sighting/128848285</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128848281</v>
+        <v>128848292</v>
       </c>
       <c r="B31" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4386,7 +4246,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514159</v>
+        <v>514148</v>
       </c>
       <c r="R31" t="n">
         <v>6583896</v>
@@ -4416,17 +4276,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4457,43 +4317,43 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848281</t>
+          <t>https://artportalen.se/Sighting/128848292</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128848287</v>
+        <v>128848254</v>
       </c>
       <c r="B32" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4508,7 +4368,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4517,13 +4377,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514153</v>
+        <v>514136</v>
       </c>
       <c r="R32" t="n">
-        <v>6583896</v>
+        <v>6583960</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4547,22 +4407,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4588,16 +4448,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848287</t>
+          <t>https://artportalen.se/Sighting/128848254</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128848264</v>
+        <v>128848268</v>
       </c>
       <c r="B33" t="n">
-        <v>56840</v>
+        <v>56835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4605,26 +4465,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206000</v>
+        <v>205995</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4634,7 +4494,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>aktiv</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4696,11 +4556,6 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Sociala ljud/spelsång</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4724,43 +4579,43 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848264</t>
+          <t>https://artportalen.se/Sighting/128848268</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128848259</v>
+        <v>128848283</v>
       </c>
       <c r="B34" t="n">
-        <v>56837</v>
+        <v>56835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4775,7 +4630,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ultraljudsdetektor</t>
+          <t>autobox</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4784,13 +4639,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514136</v>
+        <v>514157</v>
       </c>
       <c r="R34" t="n">
-        <v>6583960</v>
+        <v>6583896</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4814,22 +4669,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,43 +4710,43 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848259</t>
+          <t>https://artportalen.se/Sighting/128848283</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128848280</v>
+        <v>128848290</v>
       </c>
       <c r="B35" t="n">
-        <v>56837</v>
+        <v>56835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4915,7 +4770,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514160</v>
+        <v>514151</v>
       </c>
       <c r="R35" t="n">
         <v>6583896</v>
@@ -4945,17 +4800,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4986,16 +4841,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128848280</t>
+          <t>https://artportalen.se/Sighting/128848290</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128848286</v>
+        <v>128848250</v>
       </c>
       <c r="B36" t="n">
-        <v>56837</v>
+        <v>56816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5003,26 +4858,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5037,7 +4892,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>ultraljudsdetektor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5046,13 +4901,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514154</v>
+        <v>514136</v>
       </c>
       <c r="R36" t="n">
-        <v>6583896</v>
+        <v>6583960</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5076,22 +4931,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5116,6 +4971,928 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848250</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128848265</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>514046</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6583983</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848265</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128848281</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>514159</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6583896</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848281</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128848287</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>514153</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6583896</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848287</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128848264</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>514046</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6583983</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sociala ljud/spelsång</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848264</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128848259</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>514136</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6583960</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848259</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128848280</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>514160</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6583896</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848280</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128848286</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ölmbrotorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>514154</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6583896</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Axberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128848286</t>
         </is>
@@ -5158,6 +5935,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2577,7 +2577,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584143</v>
+        <v>6584142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2577,7 +2577,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584142</v>
+        <v>6584143</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58552</v>
+        <v>58565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58448</v>
+        <v>58461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58293</v>
+        <v>58306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58293</v>
+        <v>58306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58293</v>
+        <v>58306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58731</v>
+        <v>58744</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58565</v>
+        <v>58567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584143</v>
+        <v>6584142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2644,7 +2644,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58461</v>
+        <v>58463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58306</v>
+        <v>58308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58306</v>
+        <v>58308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58306</v>
+        <v>58308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58744</v>
+        <v>58746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2563,11 +2563,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -2674,11 +2670,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -2785,11 +2777,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -2896,11 +2884,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -3007,11 +2991,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -3239,11 +3219,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>
@@ -3350,11 +3326,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ölmbrotorp, Nrk</t>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2573,7 +2573,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584142</v>
+        <v>6584143</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58567</v>
+        <v>58577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584143</v>
+        <v>6584142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2640,7 +2640,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58463</v>
+        <v>58473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58308</v>
+        <v>58318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58308</v>
+        <v>58318</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58308</v>
+        <v>58318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58746</v>
+        <v>58756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584142</v>
+        <v>6584143</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2640,7 +2640,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58473</v>
+        <v>58474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58318</v>
+        <v>58319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58318</v>
+        <v>58319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58318</v>
+        <v>58319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58756</v>
+        <v>58758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58579</v>
+        <v>58581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58319</v>
+        <v>58321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58319</v>
+        <v>58321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58319</v>
+        <v>58321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58758</v>
+        <v>58760</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2573,7 +2573,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584143</v>
+        <v>6584142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 14614-2026 artfynd.xlsx
+++ b/artfynd/A 14614-2026 artfynd.xlsx
@@ -2533,7 +2533,7 @@
         <v>137010691</v>
       </c>
       <c r="B17" t="n">
-        <v>58581</v>
+        <v>58584</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>514163</v>
       </c>
       <c r="R17" t="n">
-        <v>6584143</v>
+        <v>6584142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2640,7 +2640,7 @@
         <v>137010772</v>
       </c>
       <c r="B18" t="n">
-        <v>58476</v>
+        <v>58479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137010683</v>
       </c>
       <c r="B19" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137010694</v>
       </c>
       <c r="B20" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>137010751</v>
       </c>
       <c r="B21" t="n">
-        <v>58321</v>
+        <v>58324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137010759</v>
       </c>
       <c r="B23" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>137010688</v>
       </c>
       <c r="B24" t="n">
-        <v>58760</v>
+        <v>58763</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
